--- a/DataTables/Datas/#Resource.xlsx
+++ b/DataTables/Datas/#Resource.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>##var</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Assets/_Resources/Prefab/Entity/Player/Player.prefab</t>
+  </si>
+  <si>
+    <t>Assets/_Resources/Prefab/BattleCamera/BattleCamera.prefab</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="1:3">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1049,7 +1052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="1:3">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1057,52 +1060,55 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="1:3">
       <c r="B7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:2">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="1:3">
       <c r="B9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="1:3">
       <c r="B10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="1:3">
       <c r="B11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="1:3">
       <c r="B12">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="1:3">
       <c r="B13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:2">
+    <row r="14" spans="1:3">
       <c r="B14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="1:3">
       <c r="B15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:3">
       <c r="B16">
         <v>12</v>
       </c>

--- a/DataTables/Datas/#Resource.xlsx
+++ b/DataTables/Datas/#Resource.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Assets/_Resources/Prefab/BattleCamera/BattleCamera.prefab</t>
+  </si>
+  <si>
+    <t>Assets/_Resources/Prefab/Map/Map1.prefab</t>
   </si>
 </sst>
 </file>
@@ -1072,6 +1075,9 @@
       <c r="B8">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="B9">

--- a/DataTables/Datas/#Resource.xlsx
+++ b/DataTables/Datas/#Resource.xlsx
@@ -69,7 +69,7 @@
     <t>Assets/_Resources/Prefab/BattleCamera/BattleCamera.prefab</t>
   </si>
   <si>
-    <t>Assets/_Resources/Prefab/Map/Map1.prefab</t>
+    <t>Assets/_Resources/Prefab/Map/Map1/Map1.prefab</t>
   </si>
 </sst>
 </file>

--- a/DataTables/Datas/#Resource.xlsx
+++ b/DataTables/Datas/#Resource.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="18345" windowHeight="4650"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>

--- a/DataTables/Datas/#Resource.xlsx
+++ b/DataTables/Datas/#Resource.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18345" windowHeight="4650"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>##var</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Assets/_Resources/Prefab/Map/Map1/Map1.prefab</t>
+  </si>
+  <si>
+    <t>Assets/_Resources/Prefab/Entity/Monster/Enemy2.prefab</t>
   </si>
 </sst>
 </file>
@@ -1083,6 +1086,9 @@
       <c r="B9">
         <v>5</v>
       </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="B10">
